--- a/event_registration_forms/021_student_conference_time_preference_form--event_registration_forms.xlsx
+++ b/event_registration_forms/021_student_conference_time_preference_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>start_time_1</t>
+          <t>start_time</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>start_time</t>
+          <t>What time do you want the event to start?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,35 +543,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>start_time_2</t>
+          <t>end_time</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>start_time</t>
+          <t>What time do you want the event to end?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>end_time_1</t>
+          <t>preferred_language</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>end_time</t>
+          <t>What is your preferred language?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>end_time_2</t>
+          <t>required_languages</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>end_time</t>
+          <t>Which languages do you require?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>preferred_language</t>
+          <t>available_time_slots</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>preferred_language</t>
+          <t>Which time slots are available?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>required_languages</t>
+          <t>available_time_slots_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>required_languages</t>
+          <t>Available Time Slots 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>required_languages_1</t>
+          <t>available_time_slots_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>required_languages</t>
+          <t>Available Time Slots 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,40 +676,40 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>available_time_slots</t>
+          <t>schedule_preferences</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>available_time_slots</t>
+          <t>What are your schedule preferences?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>available_time_slots_1</t>
+          <t>schedule_preferences_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>available_time_slots</t>
+          <t>Schedule Preferences 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>schedule_preferences</t>
+          <t>schedule_preferences_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>schedule_preferences</t>
+          <t>Schedule Preferences 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>schedule_preferences_1</t>
+          <t>schedule_preferences_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>schedule_preferences_1</t>
+          <t>Schedule Preferences 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,16 +773,154 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>schedule_preferences_2</t>
+          <t>schedule_preferences_4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>schedule_preferences_2</t>
+          <t>Schedule Preferences 4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>schedule_preferences_5</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Schedule Preferences 5</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>schedule_preferences_6</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Schedule Preferences 6</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>schedule_preferences_7</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Schedule Preferences 7</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>schedule_preferences_8</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Schedule Preferences 8</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>schedule_preferences_9</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Schedule Preferences 9</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>schedule_preferences_10</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Schedule Preferences 10</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -799,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -878,170 +1016,476 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>required_languages_choices</t>
+          <t>preferred_language_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>english</t>
+          <t>german</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>German</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>required_languages_choices</t>
+          <t>preferred_language_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>french</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>French</t>
+          <t>Chinese</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>required_languages_1_choices</t>
+          <t>preferred_language_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>french</t>
+          <t>portuguese</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>French</t>
+          <t>Portuguese</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>required_languages_1_choices</t>
+          <t>preferred_language_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>spanish</t>
+          <t>arabic</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>Arabic</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>available_time_slots_choices</t>
+          <t>preferred_language_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8:00-09:00</t>
+          <t>russian</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>8:00-09:00</t>
+          <t>Russian</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>available_time_slots_choices</t>
+          <t>preferred_language_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>09:00-10:00</t>
+          <t>japanese</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>09:00-10:00</t>
+          <t>Japanese</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>available_time_slots_choices</t>
+          <t>required_languages_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10:00-11:00</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>10:00-11:00</t>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>available_time_slots_1_choices</t>
+          <t>required_languages_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10:00-11:00</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10:00-11:00</t>
+          <t>French</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>available_time_slots_1_choices</t>
+          <t>required_languages_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:00-12:00</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>11:00-12:00</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>required_languages_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>german</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>German</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>required_languages_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Chinese</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>required_languages_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>portuguese</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Portuguese</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>required_languages_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>russian</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Russian</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>available_time_slots_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>08:00-09:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>08:00-09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>available_time_slots_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>09:00-10:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>09:00-10:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>available_time_slots_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>10:00-11:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>10:00-11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>available_time_slots_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>11:00-12:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>11:00-12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>available_time_slots_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>12:00-13:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>12:00-13:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>available_time_slots_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>13:00-14:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>13:00-14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>available_time_slots_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>14:00-15:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>14:00-15:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>available_time_slots_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>15:00-16:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>15:00-16:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>available_time_slots_1_choices</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>10:00-11:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>10:00-11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>available_time_slots_1_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>11:00-12:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>11:00-12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>available_time_slots_1_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t>12:00-13:00</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>12:00-13:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>available_time_slots_1_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>13:00-14:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>13:00-14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>available_time_slots_1_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>14:00-15:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>14:00-15:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>available_time_slots_2_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>12:00-13:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>12:00-13:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>available_time_slots_2_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>13:00-14:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>13:00-14:00</t>
         </is>
       </c>
     </row>
